--- a/public/excel_downloads/Appium_Test_Report.xlsx
+++ b/public/excel_downloads/Appium_Test_Report.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F511"/>
+  <dimension ref="A1:G511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Duration MS</t>
+          <t>Execution Time</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
         </is>
       </c>
     </row>
@@ -511,6 +516,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -543,6 +553,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -575,6 +590,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -607,6 +627,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -639,6 +664,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -671,6 +701,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -703,6 +738,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -735,6 +775,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -767,6 +812,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -799,6 +849,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -831,6 +886,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -863,6 +923,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -895,6 +960,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -927,6 +997,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -959,6 +1034,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -991,6 +1071,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1023,6 +1108,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1055,6 +1145,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1087,6 +1182,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1119,6 +1219,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1151,6 +1256,11 @@
           <t>319.2 ms</t>
         </is>
       </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1183,6 +1293,11 @@
           <t>334.4 ms</t>
         </is>
       </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1215,6 +1330,11 @@
           <t>349.6 ms</t>
         </is>
       </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1247,6 +1367,11 @@
           <t>364.8 ms</t>
         </is>
       </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1279,6 +1404,11 @@
           <t>380.0 ms</t>
         </is>
       </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1311,6 +1441,11 @@
           <t>395.2 ms</t>
         </is>
       </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1343,6 +1478,11 @@
           <t>410.4 ms</t>
         </is>
       </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1375,6 +1515,11 @@
           <t>425.6 ms</t>
         </is>
       </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1407,6 +1552,11 @@
           <t>440.8 ms</t>
         </is>
       </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1439,6 +1589,11 @@
           <t>456.0 ms</t>
         </is>
       </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1471,6 +1626,11 @@
           <t>471.2 ms</t>
         </is>
       </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1503,6 +1663,11 @@
           <t>486.4 ms</t>
         </is>
       </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1535,6 +1700,11 @@
           <t>501.6 ms</t>
         </is>
       </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1567,6 +1737,11 @@
           <t>516.8 ms</t>
         </is>
       </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1599,6 +1774,11 @@
           <t>532.0 ms</t>
         </is>
       </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1631,6 +1811,11 @@
           <t>547.2 ms</t>
         </is>
       </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1663,6 +1848,11 @@
           <t>562.4 ms</t>
         </is>
       </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1695,6 +1885,11 @@
           <t>577.6 ms</t>
         </is>
       </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1727,6 +1922,11 @@
           <t>592.8 ms</t>
         </is>
       </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1759,6 +1959,11 @@
           <t>608.0 ms</t>
         </is>
       </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1791,6 +1996,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1823,6 +2033,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1855,6 +2070,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1887,6 +2107,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1919,6 +2144,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1951,6 +2181,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1983,6 +2218,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2015,6 +2255,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -2047,6 +2292,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2079,6 +2329,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2111,6 +2366,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2143,6 +2403,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2175,6 +2440,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -2207,6 +2477,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -2239,6 +2514,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -2271,6 +2551,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -2303,6 +2588,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -2335,6 +2625,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -2367,6 +2662,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -2399,6 +2699,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -2431,6 +2736,11 @@
           <t>319.2 ms</t>
         </is>
       </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -2463,6 +2773,11 @@
           <t>334.4 ms</t>
         </is>
       </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -2495,6 +2810,11 @@
           <t>349.6 ms</t>
         </is>
       </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -2527,6 +2847,11 @@
           <t>364.8 ms</t>
         </is>
       </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -2559,6 +2884,11 @@
           <t>380.0 ms</t>
         </is>
       </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -2591,6 +2921,11 @@
           <t>395.2 ms</t>
         </is>
       </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2623,6 +2958,11 @@
           <t>410.4 ms</t>
         </is>
       </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2655,6 +2995,11 @@
           <t>425.6 ms</t>
         </is>
       </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2687,6 +3032,11 @@
           <t>440.8 ms</t>
         </is>
       </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2719,6 +3069,11 @@
           <t>456.0 ms</t>
         </is>
       </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2751,6 +3106,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2783,6 +3143,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2815,6 +3180,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2847,6 +3217,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2879,6 +3254,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2911,6 +3291,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2943,6 +3328,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2975,6 +3365,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3007,6 +3402,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -3039,6 +3439,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -3071,6 +3476,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3103,6 +3513,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -3135,6 +3550,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -3167,6 +3587,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -3199,6 +3624,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -3231,6 +3661,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3263,6 +3698,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -3295,6 +3735,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3327,6 +3772,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -3359,6 +3809,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3391,6 +3846,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -3423,6 +3883,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3455,6 +3920,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3487,6 +3957,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -3519,6 +3994,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3551,6 +4031,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3583,6 +4068,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -3615,6 +4105,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -3647,6 +4142,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -3679,6 +4179,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -3711,6 +4216,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -3743,6 +4253,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -3775,6 +4290,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3807,6 +4327,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3839,6 +4364,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -3871,6 +4401,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -3903,6 +4438,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -3935,6 +4475,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -3967,6 +4512,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -3999,6 +4549,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4031,6 +4586,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -4063,6 +4623,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -4095,6 +4660,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4127,6 +4697,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -4159,6 +4734,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -4191,6 +4771,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -4223,6 +4808,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -4255,6 +4845,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -4287,6 +4882,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -4319,6 +4919,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -4351,6 +4956,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -4383,6 +4993,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -4415,6 +5030,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -4447,6 +5067,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -4479,6 +5104,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -4511,6 +5141,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -4543,6 +5178,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -4575,6 +5215,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -4607,6 +5252,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -4639,6 +5289,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -4671,6 +5326,11 @@
           <t>319.2 ms</t>
         </is>
       </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -4703,6 +5363,11 @@
           <t>334.4 ms</t>
         </is>
       </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -4735,6 +5400,11 @@
           <t>349.6 ms</t>
         </is>
       </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -4767,6 +5437,11 @@
           <t>364.8 ms</t>
         </is>
       </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -4799,6 +5474,11 @@
           <t>380.0 ms</t>
         </is>
       </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -4831,6 +5511,11 @@
           <t>395.2 ms</t>
         </is>
       </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -4863,6 +5548,11 @@
           <t>410.4 ms</t>
         </is>
       </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -4895,6 +5585,11 @@
           <t>425.6 ms</t>
         </is>
       </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -4927,6 +5622,11 @@
           <t>440.8 ms</t>
         </is>
       </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -4959,6 +5659,11 @@
           <t>456.0 ms</t>
         </is>
       </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -4991,6 +5696,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -5023,6 +5733,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -5055,6 +5770,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -5087,6 +5807,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -5119,6 +5844,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -5151,6 +5881,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -5183,6 +5918,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -5215,6 +5955,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -5247,6 +5992,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -5279,6 +6029,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -5311,6 +6066,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -5343,6 +6103,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -5375,6 +6140,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -5407,6 +6177,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -5439,6 +6214,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -5471,6 +6251,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -5503,6 +6288,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -5535,6 +6325,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -5567,6 +6362,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -5599,6 +6399,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -5631,6 +6436,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -5663,6 +6473,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -5695,6 +6510,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -5727,6 +6547,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -5759,6 +6584,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -5791,6 +6621,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -5823,6 +6658,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -5855,6 +6695,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -5887,6 +6732,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -5919,6 +6769,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -5951,6 +6806,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -5983,6 +6843,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -6015,6 +6880,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -6047,6 +6917,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -6079,6 +6954,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -6111,6 +6991,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -6143,6 +7028,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -6175,6 +7065,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -6207,6 +7102,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -6239,6 +7139,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -6271,6 +7176,11 @@
           <t>319.2 ms</t>
         </is>
       </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -6303,6 +7213,11 @@
           <t>334.4 ms</t>
         </is>
       </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -6335,6 +7250,11 @@
           <t>349.6 ms</t>
         </is>
       </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -6367,6 +7287,11 @@
           <t>364.8 ms</t>
         </is>
       </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -6399,6 +7324,11 @@
           <t>380.0 ms</t>
         </is>
       </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -6431,6 +7361,11 @@
           <t>395.2 ms</t>
         </is>
       </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -6463,6 +7398,11 @@
           <t>410.4 ms</t>
         </is>
       </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -6495,6 +7435,11 @@
           <t>425.6 ms</t>
         </is>
       </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -6527,6 +7472,11 @@
           <t>440.8 ms</t>
         </is>
       </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -6559,6 +7509,11 @@
           <t>456.0 ms</t>
         </is>
       </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -6591,6 +7546,11 @@
           <t>471.2 ms</t>
         </is>
       </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -6623,6 +7583,11 @@
           <t>486.4 ms</t>
         </is>
       </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -6655,6 +7620,11 @@
           <t>501.6 ms</t>
         </is>
       </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -6687,6 +7657,11 @@
           <t>516.8 ms</t>
         </is>
       </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -6719,6 +7694,11 @@
           <t>532.0 ms</t>
         </is>
       </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -6751,6 +7731,11 @@
           <t>547.2 ms</t>
         </is>
       </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -6783,6 +7768,11 @@
           <t>562.4 ms</t>
         </is>
       </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -6815,6 +7805,11 @@
           <t>577.6 ms</t>
         </is>
       </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -6847,6 +7842,11 @@
           <t>592.8 ms</t>
         </is>
       </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -6879,6 +7879,11 @@
           <t>608.0 ms</t>
         </is>
       </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -6911,6 +7916,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -6943,6 +7953,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -6975,6 +7990,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -7007,6 +8027,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -7039,6 +8064,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -7071,6 +8101,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -7103,6 +8138,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -7135,6 +8175,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -7167,6 +8212,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -7199,6 +8249,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -7231,6 +8286,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -7263,6 +8323,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -7295,6 +8360,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -7327,6 +8397,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -7359,6 +8434,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -7391,6 +8471,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -7423,6 +8508,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -7455,6 +8545,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -7487,6 +8582,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -7519,6 +8619,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -7551,6 +8656,11 @@
           <t>319.2 ms</t>
         </is>
       </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -7583,6 +8693,11 @@
           <t>334.4 ms</t>
         </is>
       </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -7615,6 +8730,11 @@
           <t>349.6 ms</t>
         </is>
       </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -7647,6 +8767,11 @@
           <t>364.8 ms</t>
         </is>
       </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -7679,6 +8804,11 @@
           <t>380.0 ms</t>
         </is>
       </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -7711,6 +8841,11 @@
           <t>395.2 ms</t>
         </is>
       </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -7743,6 +8878,11 @@
           <t>410.4 ms</t>
         </is>
       </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -7775,6 +8915,11 @@
           <t>425.6 ms</t>
         </is>
       </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -7807,6 +8952,11 @@
           <t>440.8 ms</t>
         </is>
       </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -7839,6 +8989,11 @@
           <t>456.0 ms</t>
         </is>
       </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -7871,6 +9026,11 @@
           <t>471.2 ms</t>
         </is>
       </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -7903,6 +9063,11 @@
           <t>486.4 ms</t>
         </is>
       </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -7935,6 +9100,11 @@
           <t>501.6 ms</t>
         </is>
       </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -7967,6 +9137,11 @@
           <t>516.8 ms</t>
         </is>
       </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -7999,6 +9174,11 @@
           <t>532.0 ms</t>
         </is>
       </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -8031,6 +9211,11 @@
           <t>547.2 ms</t>
         </is>
       </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -8063,6 +9248,11 @@
           <t>562.4 ms</t>
         </is>
       </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -8095,6 +9285,11 @@
           <t>577.6 ms</t>
         </is>
       </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -8127,6 +9322,11 @@
           <t>592.8 ms</t>
         </is>
       </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -8159,6 +9359,11 @@
           <t>608.0 ms</t>
         </is>
       </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -8191,6 +9396,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -8223,6 +9433,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -8255,6 +9470,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -8287,6 +9507,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -8319,6 +9544,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -8351,6 +9581,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -8383,6 +9618,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -8415,6 +9655,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -8447,6 +9692,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -8479,6 +9729,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -8511,6 +9766,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -8543,6 +9803,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -8575,6 +9840,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -8607,6 +9877,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -8639,6 +9914,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -8671,6 +9951,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -8703,6 +9988,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -8735,6 +10025,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -8767,6 +10062,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -8799,6 +10099,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -8831,6 +10136,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -8863,6 +10173,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -8895,6 +10210,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -8927,6 +10247,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -8959,6 +10284,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -8991,6 +10321,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -9023,6 +10358,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -9055,6 +10395,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -9087,6 +10432,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -9119,6 +10469,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -9151,6 +10506,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -9183,6 +10543,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -9215,6 +10580,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -9247,6 +10617,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -9279,6 +10654,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -9311,6 +10691,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -9343,6 +10728,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -9375,6 +10765,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -9407,6 +10802,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -9439,6 +10839,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -9471,6 +10876,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -9503,6 +10913,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -9535,6 +10950,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -9567,6 +10987,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -9599,6 +11024,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -9631,6 +11061,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -9663,6 +11098,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -9695,6 +11135,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -9727,6 +11172,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -9759,6 +11209,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -9791,6 +11246,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -9823,6 +11283,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -9855,6 +11320,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -9887,6 +11357,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -9919,6 +11394,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -9951,6 +11431,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -9983,6 +11468,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -10015,6 +11505,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -10047,6 +11542,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -10079,6 +11579,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -10111,6 +11616,11 @@
           <t>319.2 ms</t>
         </is>
       </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -10143,6 +11653,11 @@
           <t>334.4 ms</t>
         </is>
       </c>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -10175,6 +11690,11 @@
           <t>349.6 ms</t>
         </is>
       </c>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -10207,6 +11727,11 @@
           <t>364.8 ms</t>
         </is>
       </c>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -10239,6 +11764,11 @@
           <t>380.0 ms</t>
         </is>
       </c>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -10271,6 +11801,11 @@
           <t>395.2 ms</t>
         </is>
       </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -10303,6 +11838,11 @@
           <t>410.4 ms</t>
         </is>
       </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -10335,6 +11875,11 @@
           <t>425.6 ms</t>
         </is>
       </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -10367,6 +11912,11 @@
           <t>440.8 ms</t>
         </is>
       </c>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -10399,6 +11949,11 @@
           <t>456.0 ms</t>
         </is>
       </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -10431,6 +11986,11 @@
           <t>471.2 ms</t>
         </is>
       </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -10463,6 +12023,11 @@
           <t>486.4 ms</t>
         </is>
       </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -10495,6 +12060,11 @@
           <t>501.6 ms</t>
         </is>
       </c>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -10527,6 +12097,11 @@
           <t>516.8 ms</t>
         </is>
       </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -10559,6 +12134,11 @@
           <t>532.0 ms</t>
         </is>
       </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -10591,6 +12171,11 @@
           <t>547.2 ms</t>
         </is>
       </c>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -10623,6 +12208,11 @@
           <t>562.4 ms</t>
         </is>
       </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -10655,6 +12245,11 @@
           <t>577.6 ms</t>
         </is>
       </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -10687,6 +12282,11 @@
           <t>592.8 ms</t>
         </is>
       </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -10719,6 +12319,11 @@
           <t>608.0 ms</t>
         </is>
       </c>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -10751,6 +12356,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -10783,6 +12393,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -10815,6 +12430,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -10847,6 +12467,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -10879,6 +12504,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -10911,6 +12541,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -10943,6 +12578,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -10975,6 +12615,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -11007,6 +12652,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -11039,6 +12689,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -11071,6 +12726,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -11103,6 +12763,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -11135,6 +12800,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -11167,6 +12837,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -11199,6 +12874,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -11231,6 +12911,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -11263,6 +12948,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -11295,6 +12985,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -11327,6 +13022,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -11359,6 +13059,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -11391,6 +13096,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -11423,6 +13133,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -11455,6 +13170,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -11487,6 +13207,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -11519,6 +13244,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -11551,6 +13281,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -11583,6 +13318,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -11615,6 +13355,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -11647,6 +13392,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -11679,6 +13429,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -11711,6 +13466,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -11743,6 +13503,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -11775,6 +13540,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -11807,6 +13577,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -11839,6 +13614,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -11871,6 +13651,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -11903,6 +13688,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -11935,6 +13725,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -11967,6 +13762,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -11999,6 +13799,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -12031,6 +13836,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -12063,6 +13873,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -12095,6 +13910,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -12127,6 +13947,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -12159,6 +13984,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -12191,6 +14021,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -12223,6 +14058,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -12255,6 +14095,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -12287,6 +14132,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -12319,6 +14169,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -12351,6 +14206,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -12383,6 +14243,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -12415,6 +14280,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -12447,6 +14317,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -12479,6 +14354,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -12511,6 +14391,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -12543,6 +14428,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -12575,6 +14465,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -12607,6 +14502,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -12639,6 +14539,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -12671,6 +14576,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -12703,6 +14613,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -12735,6 +14650,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -12767,6 +14687,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -12799,6 +14724,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -12831,6 +14761,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -12863,6 +14798,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -12895,6 +14835,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -12927,6 +14872,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -12959,6 +14909,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -12991,6 +14946,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -13023,6 +14983,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -13055,6 +15020,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -13087,6 +15057,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -13119,6 +15094,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -13151,6 +15131,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -13183,6 +15168,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -13215,6 +15205,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -13247,6 +15242,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -13279,6 +15279,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -13311,6 +15316,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -13343,6 +15353,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -13375,6 +15390,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -13407,6 +15427,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -13439,6 +15464,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -13471,6 +15501,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -13503,6 +15538,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -13535,6 +15575,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -13567,6 +15612,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -13599,6 +15649,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -13631,6 +15686,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -13663,6 +15723,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -13695,6 +15760,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -13727,6 +15797,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -13759,6 +15834,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -13791,6 +15871,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -13823,6 +15908,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -13855,6 +15945,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -13887,6 +15982,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -13919,6 +16019,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -13951,6 +16056,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -13983,6 +16093,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -14015,6 +16130,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -14047,6 +16167,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -14079,6 +16204,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -14111,6 +16241,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -14143,6 +16278,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -14175,6 +16315,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -14207,6 +16352,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -14239,6 +16389,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -14271,6 +16426,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -14303,6 +16463,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -14335,6 +16500,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -14367,6 +16537,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -14399,6 +16574,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -14431,6 +16611,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -14463,6 +16648,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -14495,6 +16685,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -14527,6 +16722,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -14559,6 +16759,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -14591,6 +16796,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -14623,6 +16833,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -14655,6 +16870,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -14687,6 +16907,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -14719,6 +16944,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -14751,6 +16981,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -14783,6 +17018,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -14815,6 +17055,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -14847,6 +17092,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -14879,6 +17129,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -14911,6 +17166,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -14943,6 +17203,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -14975,6 +17240,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -15007,6 +17277,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -15039,6 +17314,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -15071,6 +17351,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -15103,6 +17388,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -15135,6 +17425,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -15167,6 +17462,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -15199,6 +17499,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -15231,6 +17536,11 @@
           <t>15.2 ms</t>
         </is>
       </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -15263,6 +17573,11 @@
           <t>30.4 ms</t>
         </is>
       </c>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -15295,6 +17610,11 @@
           <t>45.6 ms</t>
         </is>
       </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -15327,6 +17647,11 @@
           <t>60.8 ms</t>
         </is>
       </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -15359,6 +17684,11 @@
           <t>76.0 ms</t>
         </is>
       </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -15391,6 +17721,11 @@
           <t>91.2 ms</t>
         </is>
       </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -15423,6 +17758,11 @@
           <t>106.4 ms</t>
         </is>
       </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -15455,6 +17795,11 @@
           <t>121.6 ms</t>
         </is>
       </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -15487,6 +17832,11 @@
           <t>136.8 ms</t>
         </is>
       </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -15519,6 +17869,11 @@
           <t>152.0 ms</t>
         </is>
       </c>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -15551,6 +17906,11 @@
           <t>167.2 ms</t>
         </is>
       </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -15583,6 +17943,11 @@
           <t>182.4 ms</t>
         </is>
       </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -15615,6 +17980,11 @@
           <t>197.6 ms</t>
         </is>
       </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -15647,6 +18017,11 @@
           <t>212.8 ms</t>
         </is>
       </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
@@ -15679,6 +18054,11 @@
           <t>228.0 ms</t>
         </is>
       </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
@@ -15711,6 +18091,11 @@
           <t>243.2 ms</t>
         </is>
       </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
@@ -15743,6 +18128,11 @@
           <t>258.4 ms</t>
         </is>
       </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
@@ -15775,6 +18165,11 @@
           <t>273.6 ms</t>
         </is>
       </c>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
@@ -15807,6 +18202,11 @@
           <t>288.8 ms</t>
         </is>
       </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
@@ -15839,6 +18239,11 @@
           <t>304.0 ms</t>
         </is>
       </c>
+      <c r="G481" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
@@ -15871,6 +18276,11 @@
           <t>319.2 ms</t>
         </is>
       </c>
+      <c r="G482" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
@@ -15903,6 +18313,11 @@
           <t>334.4 ms</t>
         </is>
       </c>
+      <c r="G483" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
@@ -15935,6 +18350,11 @@
           <t>349.6 ms</t>
         </is>
       </c>
+      <c r="G484" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
@@ -15967,6 +18387,11 @@
           <t>364.8 ms</t>
         </is>
       </c>
+      <c r="G485" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
@@ -15999,6 +18424,11 @@
           <t>380.0 ms</t>
         </is>
       </c>
+      <c r="G486" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
@@ -16031,6 +18461,11 @@
           <t>395.2 ms</t>
         </is>
       </c>
+      <c r="G487" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
@@ -16063,6 +18498,11 @@
           <t>410.4 ms</t>
         </is>
       </c>
+      <c r="G488" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
@@ -16095,6 +18535,11 @@
           <t>425.6 ms</t>
         </is>
       </c>
+      <c r="G489" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
@@ -16127,6 +18572,11 @@
           <t>440.8 ms</t>
         </is>
       </c>
+      <c r="G490" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -16159,6 +18609,11 @@
           <t>456.0 ms</t>
         </is>
       </c>
+      <c r="G491" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -16191,6 +18646,11 @@
           <t>471.2 ms</t>
         </is>
       </c>
+      <c r="G492" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
@@ -16223,6 +18683,11 @@
           <t>486.4 ms</t>
         </is>
       </c>
+      <c r="G493" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -16255,6 +18720,11 @@
           <t>501.6 ms</t>
         </is>
       </c>
+      <c r="G494" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="inlineStr">
@@ -16287,6 +18757,11 @@
           <t>516.8 ms</t>
         </is>
       </c>
+      <c r="G495" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="inlineStr">
@@ -16319,6 +18794,11 @@
           <t>532.0 ms</t>
         </is>
       </c>
+      <c r="G496" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="2" t="inlineStr">
@@ -16351,6 +18831,11 @@
           <t>547.2 ms</t>
         </is>
       </c>
+      <c r="G497" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -16383,6 +18868,11 @@
           <t>562.4 ms</t>
         </is>
       </c>
+      <c r="G498" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="2" t="inlineStr">
@@ -16415,6 +18905,11 @@
           <t>577.6 ms</t>
         </is>
       </c>
+      <c r="G499" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="inlineStr">
@@ -16447,6 +18942,11 @@
           <t>592.8 ms</t>
         </is>
       </c>
+      <c r="G500" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="inlineStr">
@@ -16479,6 +18979,11 @@
           <t>608.0 ms</t>
         </is>
       </c>
+      <c r="G501" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="inlineStr">
@@ -16511,6 +19016,11 @@
           <t>623.2 ms</t>
         </is>
       </c>
+      <c r="G502" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="2" t="inlineStr">
@@ -16543,6 +19053,11 @@
           <t>638.4 ms</t>
         </is>
       </c>
+      <c r="G503" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="2" t="inlineStr">
@@ -16575,6 +19090,11 @@
           <t>653.6 ms</t>
         </is>
       </c>
+      <c r="G504" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="inlineStr">
@@ -16607,6 +19127,11 @@
           <t>668.8 ms</t>
         </is>
       </c>
+      <c r="G505" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="inlineStr">
@@ -16639,6 +19164,11 @@
           <t>684.0 ms</t>
         </is>
       </c>
+      <c r="G506" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="inlineStr">
@@ -16671,6 +19201,11 @@
           <t>699.2 ms</t>
         </is>
       </c>
+      <c r="G507" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="2" t="inlineStr">
@@ -16703,6 +19238,11 @@
           <t>714.4 ms</t>
         </is>
       </c>
+      <c r="G508" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="2" t="inlineStr">
@@ -16735,6 +19275,11 @@
           <t>729.6 ms</t>
         </is>
       </c>
+      <c r="G509" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="inlineStr">
@@ -16767,6 +19312,11 @@
           <t>744.8 ms</t>
         </is>
       </c>
+      <c r="G510" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="inlineStr">
@@ -16797,6 +19347,11 @@
       <c r="F511" s="2" t="inlineStr">
         <is>
           <t>760.0 ms</t>
+        </is>
+      </c>
+      <c r="G511" s="2" t="inlineStr">
+        <is>
+          <t>Mobile UI element rendered and assertion verified</t>
         </is>
       </c>
     </row>
